--- a/data/master_lorry.xlsx
+++ b/data/master_lorry.xlsx
@@ -455,10 +455,10 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C2" t="n">
-        <v>22000</v>
+        <v>23000</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/data/master_lorry.xlsx
+++ b/data/master_lorry.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F27"/>
+  <dimension ref="A1:F24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -731,23 +731,23 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>VJN8929</t>
+          <t>WA6899M</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>14.839</v>
+        <v>13.948</v>
       </c>
       <c r="C12" t="n">
-        <v>14839</v>
+        <v>13948</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>VIVIAN</t>
+          <t>SPARE</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>VIVIAN</t>
+          <t>SPARE</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -759,23 +759,23 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>BPR9226</t>
+          <t>BMN3682</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>14.377</v>
+        <v>9.074999999999999</v>
       </c>
       <c r="C13" t="n">
-        <v>14377</v>
+        <v>9075</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>VIVIAN</t>
+          <t>SPARE</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>VIVIAN</t>
+          <t>SPARE</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -787,23 +787,23 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>WA9225H</t>
+          <t>WLD8738</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>14.014</v>
+        <v>4.4</v>
       </c>
       <c r="C14" t="n">
-        <v>14014</v>
+        <v>4400</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>VIVIAN</t>
+          <t>SPARE</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>VIVIAN</t>
+          <t>SPARE</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -815,23 +815,23 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>VJA7981</t>
+          <t>VQC5311</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>10.505</v>
+        <v>1.2947</v>
       </c>
       <c r="C15" t="n">
-        <v>10505</v>
+        <v>1294.7</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>VIVIAN</t>
+          <t>SPARE</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>VIVIAN</t>
+          <t>SPARE</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -843,14 +843,14 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>VNL6819</t>
+          <t>VJN8929</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>10.879</v>
+        <v>14.839</v>
       </c>
       <c r="C16" t="n">
-        <v>10879</v>
+        <v>14839</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -871,14 +871,14 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>BPE9878</t>
+          <t>BPR9226</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>4.84</v>
+        <v>14.377</v>
       </c>
       <c r="C17" t="n">
-        <v>4840</v>
+        <v>14377</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -899,14 +899,14 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>VCC3998</t>
+          <t>WA9225H</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>4.576</v>
+        <v>14.014</v>
       </c>
       <c r="C18" t="n">
-        <v>4576</v>
+        <v>14014</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -927,14 +927,14 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>WYS5281</t>
+          <t>VJA7981</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>4.4</v>
+        <v>10.505</v>
       </c>
       <c r="C19" t="n">
-        <v>4400</v>
+        <v>10505</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -955,14 +955,14 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>VKN8836</t>
+          <t>VNL6819</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>1.199</v>
+        <v>10.879</v>
       </c>
       <c r="C20" t="n">
-        <v>1199</v>
+        <v>10879</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -983,23 +983,23 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>WA6899M</t>
+          <t>BPE9878</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>13.948</v>
+        <v>4.84</v>
       </c>
       <c r="C21" t="n">
-        <v>13948</v>
+        <v>4840</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>SPARE</t>
+          <t>VIVIAN</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>ABI</t>
+          <t>VIVIAN</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1011,18 +1011,18 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>BMN3682</t>
+          <t>VCC3998</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>9.074999999999999</v>
+        <v>4.576</v>
       </c>
       <c r="C22" t="n">
-        <v>9075</v>
+        <v>4576</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>SPARE</t>
+          <t>VIVIAN</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -1039,7 +1039,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>WLD8738</t>
+          <t>WYS5281</t>
         </is>
       </c>
       <c r="B23" t="n">
@@ -1050,7 +1050,7 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>SPARE</t>
+          <t>VIVIAN</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -1067,18 +1067,18 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>WWY8028</t>
+          <t>VKN8836</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>8.898999999999999</v>
+        <v>1.199</v>
       </c>
       <c r="C24" t="n">
-        <v>8899</v>
+        <v>1199</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>SELAYANG</t>
+          <t>VIVIAN</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
@@ -1087,90 +1087,6 @@
         </is>
       </c>
       <c r="F24" t="inlineStr">
-        <is>
-          <t>Available</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>WYD7184</t>
-        </is>
-      </c>
-      <c r="B25" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="C25" t="n">
-        <v>4400</v>
-      </c>
-      <c r="D25" t="inlineStr">
-        <is>
-          <t>BIG</t>
-        </is>
-      </c>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>VIVIAN</t>
-        </is>
-      </c>
-      <c r="F25" t="inlineStr">
-        <is>
-          <t>Available</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>BRL7687</t>
-        </is>
-      </c>
-      <c r="B26" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="C26" t="n">
-        <v>4400</v>
-      </c>
-      <c r="D26" t="inlineStr">
-        <is>
-          <t>BIG</t>
-        </is>
-      </c>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>VIVIAN</t>
-        </is>
-      </c>
-      <c r="F26" t="inlineStr">
-        <is>
-          <t>Available</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>VGY9249</t>
-        </is>
-      </c>
-      <c r="B27" t="n">
-        <v>4.433</v>
-      </c>
-      <c r="C27" t="n">
-        <v>4433</v>
-      </c>
-      <c r="D27" t="inlineStr">
-        <is>
-          <t>BIG</t>
-        </is>
-      </c>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>VIVIAN</t>
-        </is>
-      </c>
-      <c r="F27" t="inlineStr">
         <is>
           <t>Available</t>
         </is>
